--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M7B2_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M7B2_IN_Piura.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>0.42</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>1.89</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C13" s="29">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>67.77</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>29.92</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1920,11 +1920,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>115.3789</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1945,11 +1945,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>0.4799</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>0.42</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1970,11 +1970,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>114.899</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>99.58</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2168,11 +2168,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>115.4218</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2291,6 +2291,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2375,6 +2376,7 @@
       <c r="F11" s="17" t="inlineStr"/>
       <c r="G11" s="17" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -2419,6 +2421,7 @@
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="132" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
@@ -2704,11 +2707,11 @@
       </c>
       <c r="B14" s="32">
         <f>SUM(B10:B13)</f>
-        <v/>
+        <v>402.84</v>
       </c>
       <c r="C14" s="23">
         <f>SUM(C10:C13)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -2718,19 +2721,19 @@
       <c r="E14" s="17" t="inlineStr"/>
       <c r="F14" s="17">
         <f>ROUND(AVERAGE(F10:F13),2)</f>
-        <v/>
+        <v>16.96</v>
       </c>
       <c r="G14" s="22">
         <f>ROUND(AVERAGE(G10:G13),4)</f>
-        <v/>
+        <v>0.2968</v>
       </c>
       <c r="H14" s="23">
         <f>ROUND(AVERAGE(H10:H13),2)</f>
-        <v/>
+        <v>1.81</v>
       </c>
       <c r="I14" s="23">
         <f>ROUND(AVERAGE(I10:I13),2)</f>
-        <v/>
+        <v>99.79</v>
       </c>
     </row>
     <row r="15"/>
